--- a/artfynd/A 34667-2024 artfynd.xlsx
+++ b/artfynd/A 34667-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119834027</v>
+        <v>119834160</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759279</v>
+        <v>759257</v>
       </c>
       <c r="R2" t="n">
-        <v>7149729</v>
+        <v>7149753</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119834628</v>
+        <v>119836014</v>
       </c>
       <c r="B3" t="n">
         <v>91884</v>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
+          <t>Tornberget, Tornberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759136</v>
+        <v>758992</v>
       </c>
       <c r="R3" t="n">
-        <v>7149780</v>
+        <v>7149826</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119833980</v>
+        <v>119834628</v>
       </c>
       <c r="B4" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759278</v>
+        <v>759136</v>
       </c>
       <c r="R4" t="n">
-        <v>7149727</v>
+        <v>7149780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119836014</v>
+        <v>119833980</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tornberget, Tornberget, Vb</t>
+          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758992</v>
+        <v>759278</v>
       </c>
       <c r="R5" t="n">
-        <v>7149826</v>
+        <v>7149727</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119834160</v>
+        <v>119834027</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759257</v>
+        <v>759279</v>
       </c>
       <c r="R7" t="n">
-        <v>7149753</v>
+        <v>7149729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 34667-2024 artfynd.xlsx
+++ b/artfynd/A 34667-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119834160</v>
+        <v>119836014</v>
       </c>
       <c r="B2" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
+          <t>Tornberget, Tornberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759257</v>
+        <v>758992</v>
       </c>
       <c r="R2" t="n">
-        <v>7149753</v>
+        <v>7149826</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119836014</v>
+        <v>119834160</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,34 +803,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tornberget, Tornberget, Vb</t>
+          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758992</v>
+        <v>759257</v>
       </c>
       <c r="R3" t="n">
-        <v>7149826</v>
+        <v>7149753</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 34667-2024 artfynd.xlsx
+++ b/artfynd/A 34667-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119836014</v>
+        <v>119833980</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,38 +687,38 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tornberget, Tornberget, Vb</t>
+          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758992</v>
+        <v>759278</v>
       </c>
       <c r="R2" t="n">
-        <v>7149826</v>
+        <v>7149727</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119834160</v>
+        <v>119834628</v>
       </c>
       <c r="B3" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,21 +803,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759257</v>
+        <v>759136</v>
       </c>
       <c r="R3" t="n">
-        <v>7149753</v>
+        <v>7149780</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119834628</v>
+        <v>119834027</v>
       </c>
       <c r="B4" t="n">
         <v>91884</v>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759136</v>
+        <v>759279</v>
       </c>
       <c r="R4" t="n">
-        <v>7149780</v>
+        <v>7149729</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119833980</v>
+        <v>119836014</v>
       </c>
       <c r="B5" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,38 +1023,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
+          <t>Tornberget, Tornberget, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759278</v>
+        <v>758992</v>
       </c>
       <c r="R5" t="n">
-        <v>7149727</v>
+        <v>7149826</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119834027</v>
+        <v>119834160</v>
       </c>
       <c r="B7" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1251,21 +1251,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759279</v>
+        <v>759257</v>
       </c>
       <c r="R7" t="n">
-        <v>7149729</v>
+        <v>7149753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 34667-2024 artfynd.xlsx
+++ b/artfynd/A 34667-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119833980</v>
+        <v>119834027</v>
       </c>
       <c r="B2" t="n">
-        <v>91840</v>
+        <v>91884</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759278</v>
+        <v>759279</v>
       </c>
       <c r="R2" t="n">
-        <v>7149727</v>
+        <v>7149729</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119834628</v>
+        <v>119833980</v>
       </c>
       <c r="B3" t="n">
-        <v>91884</v>
+        <v>91840</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,25 +799,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -827,10 +827,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759136</v>
+        <v>759278</v>
       </c>
       <c r="R3" t="n">
-        <v>7149780</v>
+        <v>7149727</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,7 +899,7 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119834027</v>
+        <v>119836014</v>
       </c>
       <c r="B4" t="n">
         <v>91884</v>
@@ -935,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
+          <t>Tornberget, Tornberget, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759279</v>
+        <v>758992</v>
       </c>
       <c r="R4" t="n">
-        <v>7149729</v>
+        <v>7149826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119836014</v>
+        <v>119833961</v>
       </c>
       <c r="B5" t="n">
-        <v>91884</v>
+        <v>91832</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,34 +1027,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Tornberget, Tornberget, Vb</t>
+          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>758992</v>
+        <v>759275</v>
       </c>
       <c r="R5" t="n">
-        <v>7149826</v>
+        <v>7149722</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119833961</v>
+        <v>119834628</v>
       </c>
       <c r="B6" t="n">
-        <v>91832</v>
+        <v>91884</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759275</v>
+        <v>759136</v>
       </c>
       <c r="R6" t="n">
-        <v>7149722</v>
+        <v>7149780</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 34667-2024 artfynd.xlsx
+++ b/artfynd/A 34667-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>119834027</v>
       </c>
       <c r="B2" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -787,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119833980</v>
+        <v>119836014</v>
       </c>
       <c r="B3" t="n">
-        <v>91840</v>
+        <v>91902</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -799,38 +799,38 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
+          <t>Tornberget, Tornberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759278</v>
+        <v>758992</v>
       </c>
       <c r="R3" t="n">
-        <v>7149727</v>
+        <v>7149826</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119836014</v>
+        <v>119834628</v>
       </c>
       <c r="B4" t="n">
-        <v>91884</v>
+        <v>91902</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,14 +935,14 @@
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Tornberget, Tornberget, Vb</t>
+          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>758992</v>
+        <v>759136</v>
       </c>
       <c r="R4" t="n">
-        <v>7149826</v>
+        <v>7149780</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,7 +1014,7 @@
         <v>119833961</v>
       </c>
       <c r="B5" t="n">
-        <v>91832</v>
+        <v>91850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119834628</v>
+        <v>119834160</v>
       </c>
       <c r="B6" t="n">
-        <v>91884</v>
+        <v>91850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759136</v>
+        <v>759257</v>
       </c>
       <c r="R6" t="n">
-        <v>7149780</v>
+        <v>7149753</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119834160</v>
+        <v>119833980</v>
       </c>
       <c r="B7" t="n">
-        <v>91832</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759257</v>
+        <v>759278</v>
       </c>
       <c r="R7" t="n">
-        <v>7149753</v>
+        <v>7149727</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 34667-2024 artfynd.xlsx
+++ b/artfynd/A 34667-2024 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119834027</v>
+        <v>119836014</v>
       </c>
       <c r="B2" t="n">
         <v>91902</v>
@@ -711,14 +711,14 @@
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
+          <t>Tornberget, Tornberget, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>759279</v>
+        <v>758992</v>
       </c>
       <c r="R2" t="n">
-        <v>7149729</v>
+        <v>7149826</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119836014</v>
+        <v>119834027</v>
       </c>
       <c r="B3" t="n">
         <v>91902</v>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tornberget, Tornberget, Vb</t>
+          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>758992</v>
+        <v>759279</v>
       </c>
       <c r="R3" t="n">
-        <v>7149826</v>
+        <v>7149729</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119833961</v>
+        <v>119833980</v>
       </c>
       <c r="B5" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759275</v>
+        <v>759278</v>
       </c>
       <c r="R5" t="n">
-        <v>7149722</v>
+        <v>7149727</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,7 +1123,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119834160</v>
+        <v>119833961</v>
       </c>
       <c r="B6" t="n">
         <v>91850</v>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759257</v>
+        <v>759275</v>
       </c>
       <c r="R6" t="n">
-        <v>7149753</v>
+        <v>7149722</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119833980</v>
+        <v>119834160</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759278</v>
+        <v>759257</v>
       </c>
       <c r="R7" t="n">
-        <v>7149727</v>
+        <v>7149753</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 34667-2024 artfynd.xlsx
+++ b/artfynd/A 34667-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119836014</v>
+        <v>119833961</v>
       </c>
       <c r="B2" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,34 +691,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tornberget, Tornberget, Vb</t>
+          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>758992</v>
+        <v>759275</v>
       </c>
       <c r="R2" t="n">
-        <v>7149826</v>
+        <v>7149722</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -750,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>15:38</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +787,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119834027</v>
+        <v>119836014</v>
       </c>
       <c r="B3" t="n">
         <v>91902</v>
@@ -823,14 +823,14 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Tornrödmossamyran, Tornrödmossamyran, Vb</t>
+          <t>Tornberget, Tornberget, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>759279</v>
+        <v>758992</v>
       </c>
       <c r="R3" t="n">
-        <v>7149729</v>
+        <v>7149826</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -862,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -872,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>15:38</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119833980</v>
+        <v>119834160</v>
       </c>
       <c r="B5" t="n">
-        <v>91858</v>
+        <v>91850</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1023,25 +1023,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>4361</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759278</v>
+        <v>759257</v>
       </c>
       <c r="R5" t="n">
-        <v>7149727</v>
+        <v>7149753</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119833961</v>
+        <v>119834027</v>
       </c>
       <c r="B6" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759275</v>
+        <v>759279</v>
       </c>
       <c r="R6" t="n">
-        <v>7149722</v>
+        <v>7149729</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119834160</v>
+        <v>119833980</v>
       </c>
       <c r="B7" t="n">
-        <v>91850</v>
+        <v>91858</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4361</v>
+        <v>4364</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759257</v>
+        <v>759278</v>
       </c>
       <c r="R7" t="n">
-        <v>7149753</v>
+        <v>7149727</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 34667-2024 artfynd.xlsx
+++ b/artfynd/A 34667-2024 artfynd.xlsx
@@ -899,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119834628</v>
+        <v>119833980</v>
       </c>
       <c r="B4" t="n">
-        <v>91902</v>
+        <v>91858</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -911,25 +911,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -939,10 +939,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>759136</v>
+        <v>759278</v>
       </c>
       <c r="R4" t="n">
-        <v>7149780</v>
+        <v>7149727</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -974,7 +974,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,10 +1011,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119834160</v>
+        <v>119834628</v>
       </c>
       <c r="B5" t="n">
-        <v>91850</v>
+        <v>91902</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1027,21 +1027,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4361</v>
+        <v>5449</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Orange taggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum aurantiacum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Batsch:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1051,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>759257</v>
+        <v>759136</v>
       </c>
       <c r="R5" t="n">
-        <v>7149753</v>
+        <v>7149780</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:06</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,10 +1123,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119834027</v>
+        <v>119834160</v>
       </c>
       <c r="B6" t="n">
-        <v>91902</v>
+        <v>91850</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1139,21 +1139,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5449</v>
+        <v>4361</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Orange taggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum aurantiacum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Batsch:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1163,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>759279</v>
+        <v>759257</v>
       </c>
       <c r="R6" t="n">
-        <v>7149729</v>
+        <v>7149753</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1198,7 +1198,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>14:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,10 +1235,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119833980</v>
+        <v>119834027</v>
       </c>
       <c r="B7" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1247,25 +1247,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>759278</v>
+        <v>759279</v>
       </c>
       <c r="R7" t="n">
-        <v>7149727</v>
+        <v>7149729</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:57</t>
         </is>
       </c>
       <c r="AD7" t="b">
